--- a/commission/megan/2026-06.xlsx
+++ b/commission/megan/2026-06.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="44">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -115,6 +115,21 @@
     <t>ORD-EPL-1075</t>
   </si>
   <si>
+    <t>ADJUSTMENTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Palm Beach Equine Clinic</t>
+  </si>
+  <si>
+    <t>Late-clearing May payment (QB dep. 5/29/2026) — missed May payout, catch-up in June</t>
+  </si>
+  <si>
+    <t>CINV-EPL-1002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Adjustments subtotal</t>
+  </si>
+  <si>
     <t>GRAND TOTAL</t>
   </si>
   <si>
@@ -125,12 +140,6 @@
   </si>
   <si>
     <t>ORD-EPL-1124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Palm Beach Equine Clinic</t>
-  </si>
-  <si>
-    <t>CINV-EPL-1002</t>
   </si>
   <si>
     <t xml:space="preserve">   Pending total</t>
@@ -145,7 +154,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -201,6 +210,21 @@
     </font>
     <font>
       <color rgb="0F5E4F"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="7A5C1C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="7A5C1C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
     </font>
     <font>
       <b/>
@@ -248,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -284,17 +308,29 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -636,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -657,7 +693,7 @@
         <v>1</v>
       </c>
       <c r="H1" s="3">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1062,50 +1098,75 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="F33" s="19">
-        <v>7200</v>
-      </c>
-      <c r="H33" s="20">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="D35" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F36" s="22">
+      <c r="F35" s="20">
+        <v>2400</v>
+      </c>
+      <c r="G35" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H35" s="20">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36" s="23">
+        <v>2400</v>
+      </c>
+      <c r="H36" s="23">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37" s="25">
+        <v>9600</v>
+      </c>
+      <c r="H37" s="26">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="28">
         <v>3300</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F37" s="22">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="F38" s="23">
-        <v>5700</v>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="29">
+        <v>3300</v>
       </c>
     </row>
   </sheetData>

--- a/commission/megan/2026-06.xlsx
+++ b/commission/megan/2026-06.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="43">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -127,22 +127,19 @@
     <t>CINV-EPL-1002</t>
   </si>
   <si>
+    <t xml:space="preserve">   Tryon Equine Hospital</t>
+  </si>
+  <si>
+    <t>Approved by accounting on CRM record (QB match pending); paid on CRM Received Payments (6/24/2026)</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1124</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Adjustments subtotal</t>
   </si>
   <si>
     <t>GRAND TOTAL</t>
-  </si>
-  <si>
-    <t>Pending bank clearance (will roll forward to next month):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Tryon Equine Hospital</t>
-  </si>
-  <si>
-    <t>ORD-EPL-1124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Pending total</t>
   </si>
 </sst>
 </file>
@@ -154,7 +151,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -229,17 +226,6 @@
     <font>
       <b/>
       <sz val="12"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="7A7974"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <color rgb="7A7974"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -272,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -324,13 +310,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -672,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -693,7 +672,7 @@
         <v>1</v>
       </c>
       <c r="H1" s="3">
-        <v>960</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1124,49 +1103,45 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F36" s="23">
-        <v>2400</v>
-      </c>
-      <c r="H36" s="23">
-        <v>240</v>
+      <c r="D36" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" s="20">
+        <v>3300</v>
+      </c>
+      <c r="G36" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H36" s="20">
+        <v>330</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="F37" s="25">
-        <v>9600</v>
-      </c>
-      <c r="H37" s="26">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="A37" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="F37" s="23">
+        <v>5700</v>
+      </c>
+      <c r="H37" s="23">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="F40" s="28">
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="F41" s="29">
-        <v>3300</v>
+      <c r="F38" s="25">
+        <v>12900</v>
+      </c>
+      <c r="H38" s="26">
+        <v>1290</v>
       </c>
     </row>
   </sheetData>
